--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TI OPAUSTRO\TABLERO DE CONTROL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/FLUJO APP/APP_OPAUSTRO_OFICIAL/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7EC17AC-FED5-405C-82D3-98B940DCA5C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
   <si>
     <t>TALENTO HUMANO - SITUACION ACTUAL POR DEPARTAMENTO</t>
   </si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>VENTAS</t>
-  </si>
-  <si>
-    <t>31/05/2026</t>
   </si>
   <si>
     <t>ADMINISTRACION</t>
@@ -451,15 +448,15 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -725,7 +722,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -739,23 +736,23 @@
     <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-    </row>
-    <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+    </row>
+    <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -793,34 +790,34 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="19"/>
-    </row>
-    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
+    </row>
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
+      <c r="B4" s="16">
+        <v>46203</v>
       </c>
       <c r="C4" s="4">
         <v>79</v>
       </c>
       <c r="D4" s="4">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
@@ -833,15 +830,15 @@
       </c>
       <c r="H4" s="5">
         <f>C4-D4</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="6">
         <f>IF(C4=0,0,D4/C4)</f>
-        <v>0.98734177215189878</v>
+        <v>0.97468354430379744</v>
       </c>
       <c r="J4" s="6">
         <f>IF(D4=0,0,(F4+G4)/D4)</f>
-        <v>2.564102564102564E-2</v>
+        <v>2.5974025974025976E-2</v>
       </c>
       <c r="K4" s="6">
         <f>4%</f>
@@ -852,12 +849,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4" t="s">
         <v>15</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46203</v>
       </c>
       <c r="C5" s="4">
         <v>22</v>
@@ -895,18 +892,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46203</v>
       </c>
       <c r="C6" s="4">
         <v>29</v>
       </c>
       <c r="D6" s="4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -919,11 +916,11 @@
       </c>
       <c r="H6" s="5">
         <f>C6-D6</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="6">
         <f>IF(C6=0,0,D6/C6)</f>
-        <v>0.96551724137931039</v>
+        <v>1</v>
       </c>
       <c r="J6" s="6">
         <f>IF(D6=0,0,(F6+G6)/D6)</f>
@@ -938,9 +935,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9">
@@ -997,7 +994,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1009,27 +1006,27 @@
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+    </row>
+    <row r="2" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-    </row>
-    <row r="2" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
@@ -1038,48 +1035,48 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="19"/>
-    </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>14</v>
@@ -1112,15 +1109,15 @@
         <v>6.3291139240506333E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11">
         <v>2026</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="11">
         <v>22</v>
@@ -1150,15 +1147,15 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11">
         <v>2026</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="11">
         <v>29</v>
@@ -1188,12 +1185,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>14</v>
@@ -1226,15 +1223,15 @@
         <v>7.5949367088607597E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4">
         <v>22</v>
@@ -1264,15 +1261,15 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4">
         <v>29</v>
@@ -1302,12 +1299,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>2026</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>14</v>
@@ -1340,15 +1337,15 @@
         <v>5.0632911392405063E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11">
         <v>2026</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="11">
         <v>22</v>
@@ -1378,15 +1375,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>2026</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="11">
         <v>29</v>
@@ -1416,12 +1413,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>2026</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>14</v>
@@ -1454,15 +1451,15 @@
         <v>7.5949367088607597E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2026</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="4">
         <v>22</v>
@@ -1492,15 +1489,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D15" s="4">
         <v>29</v>
@@ -1530,12 +1527,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>2026</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>14</v>
@@ -1568,15 +1565,15 @@
         <v>5.0632911392405063E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>2026</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="11">
         <v>22</v>
@@ -1606,15 +1603,15 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>2026</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D18" s="11">
         <v>29</v>
@@ -1657,7 +1654,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1671,333 +1668,333 @@
     <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-    </row>
-    <row r="2" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="19"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="21"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>2026</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="H4" s="16">
         <v>46129</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>2026</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="H5" s="16">
         <v>46079</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="H6" s="16">
         <v>46062</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="H7" s="16">
         <v>46129</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="I8" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="H12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J12" s="3"/>
     </row>

--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/FLUJO APP/APP_OPAUSTRO_OFICIAL/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7EC17AC-FED5-405C-82D3-98B940DCA5C3}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53105A65-B28E-4535-90F1-77C0D9EDAC49}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="69">
   <si>
     <t>TALENTO HUMANO - SITUACION ACTUAL POR DEPARTAMENTO</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>Incumplimiento de procesos</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
   </si>
 </sst>
 </file>
@@ -722,7 +725,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -736,7 +739,7 @@
     <col min="12" max="12" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -752,7 +755,7 @@
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
     </row>
-    <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -790,7 +793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>13</v>
       </c>
@@ -806,7 +809,7 @@
       <c r="K3" s="20"/>
       <c r="L3" s="21"/>
     </row>
-    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
@@ -849,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -892,7 +895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -935,7 +938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
@@ -993,8 +996,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1006,7 +1009,7 @@
     <col min="11" max="11" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>18</v>
       </c>
@@ -1021,7 +1024,7 @@
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
     </row>
-    <row r="2" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>28</v>
       </c>
@@ -1071,7 +1074,7 @@
       <c r="J3" s="20"/>
       <c r="K3" s="21"/>
     </row>
-    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>2026</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>6.3291139240506333E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>2026</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>2026</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
@@ -1223,7 +1226,7 @@
         <v>7.5949367088607597E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
@@ -1261,7 +1264,7 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>2026</v>
       </c>
@@ -1337,7 +1340,7 @@
         <v>5.0632911392405063E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2026</v>
       </c>
@@ -1375,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>2026</v>
       </c>
@@ -1413,7 +1416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>2026</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>7.5949367088607597E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2026</v>
       </c>
@@ -1489,7 +1492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>2026</v>
       </c>
@@ -1527,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>2026</v>
       </c>
@@ -1565,7 +1568,7 @@
         <v>5.0632911392405063E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>2026</v>
       </c>
@@ -1603,7 +1606,7 @@
         <v>4.5454545454545456E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>2026</v>
       </c>
@@ -1639,6 +1642,120 @@
       <c r="K18" s="13">
         <f t="shared" si="2"/>
         <v>3.4482758620689655E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D19" s="11">
+        <v>77</v>
+      </c>
+      <c r="E19" s="11">
+        <v>2</v>
+      </c>
+      <c r="F19" s="11">
+        <v>2</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13">
+        <f t="shared" ref="I19:I21" si="3">IF(D19=0,0,(E19+F19)/D19)</f>
+        <v>5.1948051948051951E-2</v>
+      </c>
+      <c r="J19" s="13">
+        <f t="shared" ref="J19:J21" si="4">IF(D19=0,0,E19/D19)</f>
+        <v>2.5974025974025976E-2</v>
+      </c>
+      <c r="K19" s="13">
+        <f t="shared" ref="K19:K21" si="5">IF(D19=0,0,F19/D19)</f>
+        <v>2.5974025974025976E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" s="11">
+        <v>22</v>
+      </c>
+      <c r="E20" s="11">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11">
+        <v>0</v>
+      </c>
+      <c r="G20" s="11">
+        <v>0</v>
+      </c>
+      <c r="H20" s="11">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="13">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="11">
+        <v>29</v>
+      </c>
+      <c r="E21" s="11">
+        <v>2</v>
+      </c>
+      <c r="F21" s="11">
+        <v>2</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="13">
+        <f t="shared" si="3"/>
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="J21" s="13">
+        <f t="shared" si="4"/>
+        <v>6.8965517241379309E-2</v>
+      </c>
+      <c r="K21" s="13">
+        <f t="shared" si="5"/>
+        <v>6.8965517241379309E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1654,7 +1771,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1668,7 +1785,7 @@
     <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>34</v>
       </c>
@@ -1682,7 +1799,7 @@
       <c r="I1" s="18"/>
       <c r="J1" s="18"/>
     </row>
-    <row r="2" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -1714,7 +1831,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
         <v>42</v>
       </c>
@@ -1728,7 +1845,7 @@
       <c r="I3" s="20"/>
       <c r="J3" s="21"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>2026</v>
       </c>
@@ -1758,7 +1875,7 @@
       </c>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2026</v>
       </c>
@@ -1788,7 +1905,7 @@
       </c>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
@@ -1818,7 +1935,7 @@
       </c>
       <c r="J6" s="3"/>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
@@ -1848,7 +1965,7 @@
       </c>
       <c r="J7" s="3"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
@@ -1878,7 +1995,7 @@
       </c>
       <c r="J8" s="3"/>
     </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>2026</v>
       </c>
@@ -1908,7 +2025,7 @@
       </c>
       <c r="J9" s="3"/>
     </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>2026</v>
       </c>
@@ -1938,7 +2055,7 @@
       </c>
       <c r="J10" s="3"/>
     </row>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>2026</v>
       </c>
@@ -1968,7 +2085,7 @@
       </c>
       <c r="J11" s="3"/>
     </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>2026</v>
       </c>

--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/FLUJO APP/APP_OPAUSTRO_OFICIAL/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53105A65-B28E-4535-90F1-77C0D9EDAC49}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10ADF415-E820-4524-B9EB-F308C9A303B0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TALENTO ACTUAL" sheetId="1" r:id="rId1"/>
@@ -175,63 +175,42 @@
     <t>Amonestacion Escrita</t>
   </si>
   <si>
-    <t>Retorno de pedido sin seguimiento ala venta</t>
-  </si>
-  <si>
     <t>Moderada</t>
   </si>
   <si>
     <t>Castañeda Lara Danny Israel</t>
   </si>
   <si>
-    <t>No asiste a punto de encuentro</t>
-  </si>
-  <si>
     <t>Tixi Berrones Carlos Alberto</t>
   </si>
   <si>
     <t>Memorando</t>
   </si>
   <si>
-    <t>no asiste a trabajar el dia sabado 7</t>
-  </si>
-  <si>
     <t>Grave</t>
   </si>
   <si>
     <t>Martinez Martinez Israel Fernando</t>
   </si>
   <si>
-    <t>Fuera de Ruta</t>
-  </si>
-  <si>
     <t>Jaque de la Cruz Edison Santiago</t>
   </si>
   <si>
     <t>Supervisor</t>
   </si>
   <si>
-    <t>Impuntualidad PDE</t>
-  </si>
-  <si>
     <t>05/05/2026</t>
   </si>
   <si>
     <t>Alarcon Moreano Henry Gabriel</t>
   </si>
   <si>
-    <t>Cruce de facturas</t>
-  </si>
-  <si>
     <t>Sosa Esmeralda Andy Joel</t>
   </si>
   <si>
     <t>Bodeguero</t>
   </si>
   <si>
-    <t>Agresion Fisica</t>
-  </si>
-  <si>
     <t>Balla Avalos Wilmer Fabian</t>
   </si>
   <si>
@@ -242,6 +221,27 @@
   </si>
   <si>
     <t>JUNIO</t>
+  </si>
+  <si>
+    <t>Devolucion registrada sin seguimiento al proceso de venta</t>
+  </si>
+  <si>
+    <t>no asistencia al punto de encuentro programado</t>
+  </si>
+  <si>
+    <t>Inasistencia injustificada-sabado 7</t>
+  </si>
+  <si>
+    <t>Salida fuera de ruta asignada</t>
+  </si>
+  <si>
+    <t>Impuntualidad en el punto de encuentro</t>
+  </si>
+  <si>
+    <t>Cruce de facturas detectado</t>
+  </si>
+  <si>
+    <t>Conducto inadecuada (Agresion)</t>
   </si>
 </sst>
 </file>
@@ -1649,7 +1649,7 @@
         <v>2026</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         <v>2026</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C20" s="12" t="s">
         <v>15</v>
@@ -1725,7 +1725,7 @@
         <v>2026</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>16</v>
@@ -1865,13 +1865,13 @@
         <v>45</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="H4" s="16">
         <v>46129</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -1886,7 +1886,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>44</v>
@@ -1895,13 +1895,13 @@
         <v>45</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="H5" s="16">
         <v>46079</v>
       </c>
       <c r="I5" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -1916,22 +1916,22 @@
         <v>14</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H6" s="16">
         <v>46062</v>
       </c>
       <c r="I6" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -1946,7 +1946,7 @@
         <v>14</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>44</v>
@@ -1955,13 +1955,13 @@
         <v>45</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H7" s="16">
         <v>46129</v>
       </c>
       <c r="I7" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -1976,22 +1976,22 @@
         <v>14</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -2006,22 +2006,22 @@
         <v>14</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>44</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -2036,22 +2036,22 @@
         <v>16</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I10" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -2066,22 +2066,22 @@
         <v>16</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J11" s="3"/>
     </row>
@@ -2096,22 +2096,22 @@
         <v>16</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J12" s="3"/>
     </row>

--- a/pruebas/Gerencia/TALENTO HUMANO.xlsx
+++ b/pruebas/Gerencia/TALENTO HUMANO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/FLUJO APP/APP_OPAUSTRO_OFICIAL/Gerencia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ade4bf4107253254/OPAUSTRO DASHBOARD/TI OPAUSTRO/APP OPAUSTRO/APP OPAUSTRO/Gerencia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10ADF415-E820-4524-B9EB-F308C9A303B0}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="8_{13C18F3D-9789-42FE-A96C-D3EBD5B9B8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996977CD-B87C-4485-A8E4-AA98CA6C457C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TALENTO ACTUAL" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="77">
   <si>
     <t>TALENTO HUMANO - SITUACION ACTUAL POR DEPARTAMENTO</t>
   </si>
@@ -242,6 +242,30 @@
   </si>
   <si>
     <t>Conducto inadecuada (Agresion)</t>
+  </si>
+  <si>
+    <t>JULIO</t>
+  </si>
+  <si>
+    <t>Rivera Ramos Jose</t>
+  </si>
+  <si>
+    <t>Feijoo Bayas Daniel Antonio</t>
+  </si>
+  <si>
+    <t>Soto Altamirano Jonathan</t>
+  </si>
+  <si>
+    <t>Contento Lagua Roberto</t>
+  </si>
+  <si>
+    <t>No asiste ala reunion vespertina</t>
+  </si>
+  <si>
+    <t>Se evidenció permanencia en su domicilio durante horas laborables y falta de visita a clientes.</t>
+  </si>
+  <si>
+    <t>Adulteracion de recibo de cobro</t>
   </si>
 </sst>
 </file>
@@ -814,13 +838,13 @@
         <v>14</v>
       </c>
       <c r="B4" s="16">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C4" s="4">
         <v>79</v>
       </c>
       <c r="D4" s="4">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4" s="4">
         <v>0</v>
@@ -833,15 +857,15 @@
       </c>
       <c r="H4" s="5">
         <f>C4-D4</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="6">
         <f>IF(C4=0,0,D4/C4)</f>
-        <v>0.97468354430379744</v>
+        <v>0.94936708860759489</v>
       </c>
       <c r="J4" s="6">
         <f>IF(D4=0,0,(F4+G4)/D4)</f>
-        <v>2.5974025974025976E-2</v>
+        <v>2.6666666666666668E-2</v>
       </c>
       <c r="K4" s="6">
         <f>4%</f>
@@ -857,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="16">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C5" s="4">
         <v>22</v>
@@ -900,7 +924,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="16">
-        <v>46203</v>
+        <v>46234</v>
       </c>
       <c r="C6" s="4">
         <v>29</v>
@@ -949,7 +973,7 @@
       </c>
       <c r="D7" s="9">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E7" s="9">
         <f t="shared" si="0"/>
@@ -965,15 +989,15 @@
       </c>
       <c r="H7" s="9">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I7" s="10">
         <f>IF(C7=0,0,D7/C7)</f>
-        <v>0.98461538461538467</v>
+        <v>0.96923076923076923</v>
       </c>
       <c r="J7" s="10">
         <f>IF(D7=0,0,(F7+G7)/D7)</f>
-        <v>2.34375E-2</v>
+        <v>2.3809523809523808E-2</v>
       </c>
       <c r="K7" s="10">
         <f>4%</f>
@@ -996,7 +1020,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1758,6 +1782,120 @@
         <v>6.8965517241379309E-2</v>
       </c>
     </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="11">
+        <v>75</v>
+      </c>
+      <c r="E22" s="11">
+        <v>2</v>
+      </c>
+      <c r="F22" s="11">
+        <v>4</v>
+      </c>
+      <c r="G22" s="11">
+        <v>3</v>
+      </c>
+      <c r="H22" s="11">
+        <v>3</v>
+      </c>
+      <c r="I22" s="13">
+        <f t="shared" ref="I22:I24" si="6">IF(D22=0,0,(E22+F22)/D22)</f>
+        <v>0.08</v>
+      </c>
+      <c r="J22" s="13">
+        <f t="shared" ref="J22:J24" si="7">IF(D22=0,0,E22/D22)</f>
+        <v>2.6666666666666668E-2</v>
+      </c>
+      <c r="K22" s="13">
+        <f t="shared" ref="K22:K24" si="8">IF(D22=0,0,F22/D22)</f>
+        <v>5.3333333333333337E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" s="11">
+        <v>22</v>
+      </c>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="13">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="11">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="11">
+        <v>29</v>
+      </c>
+      <c r="E24" s="11">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11">
+        <v>0</v>
+      </c>
+      <c r="G24" s="11">
+        <v>1</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
+        <f t="shared" si="6"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="J24" s="13">
+        <f t="shared" si="7"/>
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="K24" s="13">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:K1"/>
@@ -1770,7 +1908,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2115,6 +2253,180 @@
       </c>
       <c r="J12" s="3"/>
     </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="16">
+        <v>46218</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="16">
+        <v>46218</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="16">
+        <v>46211</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="16">
+        <v>46225</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" s="16">
+        <v>46225</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" s="16">
+        <v>46225</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:J1"/>
